--- a/backend/analysis/SG_LE_Analysis.xlsx
+++ b/backend/analysis/SG_LE_Analysis.xlsx
@@ -10,9 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master LE List" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Industry Segmentation" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NTT-Only Accounts" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SAP MOVE-Only Accounts" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Both Sources (Overlap)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ops-Only Accounts" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SAP-Only Accounts" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Both (Ops + SAP)" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Priority Matrix (Top 30)" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
@@ -490,12 +490,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -525,7 +525,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>SOURCE (AUDIT TRAIL)</t>
         </is>
       </c>
     </row>
@@ -540,14 +540,14 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Combined</t>
+          <t>Ops + SAP combined</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>NTT Target List (Aashita/Ops)</t>
+          <t>Ops Target List (Aashita/NTT)</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -555,7 +555,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>SG Sheet</t>
+          <t>SG Sheet (Ops)</t>
         </is>
       </c>
     </row>
@@ -570,7 +570,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>SAP SEA MOVE LIST</t>
+          <t>SAP SEA MOVE LIST (SAP)</t>
         </is>
       </c>
     </row>
@@ -585,14 +585,14 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Cross-ref</t>
+          <t>Cross-ref (Ops + SAP)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>NTT-Only Accounts</t>
+          <t>Ops-Only Accounts</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -600,14 +600,14 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Gap Analysis</t>
+          <t>In Ops, NOT in SAP</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>SAP MOVE-Only Accounts</t>
+          <t>SAP-Only Accounts</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -615,7 +615,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Gap Analysis</t>
+          <t>In SAP, NOT in Ops</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>NTT SG SHEET BREAKDOWN</t>
+          <t>LE QUALIFICATION (&gt;$5B TURNOVER)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
@@ -636,237 +636,401 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>SAP Install Base</t>
+          <t>LE Qualified (&gt;$5B)</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>SG Sheet</t>
+          <t>Ops list</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>No SAP Install Base</t>
+          <t>Below $5B Threshold</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>SG Sheet</t>
+          <t>Ops list</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Migration Targets</t>
+          <t>Unknown (no turnover data)</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>SG Sheet</t>
+          <t>Ops list</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Managed Services Potential</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>SG Sheet</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr"/>
+      <c r="C15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Tier 1 (Urgent)</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>SG Sheet</t>
-        </is>
-      </c>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>NTT OPS SHEET BREAKDOWN</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr"/>
+      <c r="C16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>SAP Install Base</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>SG Sheet</t>
+          <t>Ops</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>No SAP Install Base</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>SG Sheet</t>
+          <t>Ops</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Unclassified Urgency</t>
+          <t>Migration Targets</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>SG Sheet</t>
+          <t>Ops</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr"/>
-      <c r="B20" s="2" t="inlineStr"/>
-      <c r="C20" s="2" t="inlineStr"/>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Managed Services Potential</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>SAP MOVE LIST (SG)</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr"/>
-      <c r="C21" s="2" t="inlineStr"/>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Tier 1 (Urgent)</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>1st MOVE</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>SAP MOVE</t>
+          <t>Ops</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2nd MOVE</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>SAP MOVE</t>
+          <t>Ops</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Unclassified Urgency</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>SAP MOVE</t>
+          <t>Ops</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Technical</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>SAP MOVE</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr"/>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>SAP MOVE LIST (SG)</t>
+        </is>
+      </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>KEY INSIGHT</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr"/>
-      <c r="C27" s="2" t="inlineStr"/>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>1st MOVE</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Only 6 accounts overlap between NTT SG list and SAP MOVE list</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr"/>
-      <c r="C28" s="2" t="inlineStr"/>
+          <t>2nd MOVE</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>109 accounts on NTT list are NOT on SAP MOVE</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr"/>
-      <c r="C29" s="2" t="inlineStr"/>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>69 accounts on SAP MOVE are NOT on NTT list</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr"/>
-      <c r="C30" s="2" t="inlineStr"/>
+          <t>Technical</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>SCORING METHODOLOGY (PRIORITY MATRIX)</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Tier 1 Urgency</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>+3 points</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Tier 2 Urgency</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>+2 points</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Tier 3 Urgency</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>+1 point</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Migration Target</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>+2 points</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Managed Services Potential</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>+1 point</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>SAP Install Base</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>+1 point</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>LE Qualified (&gt;$5B turnover)</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>+1 point</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Max Possible Score</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>8 points</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -884,13 +1048,13 @@
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="42" customWidth="1" min="5" max="5"/>
     <col width="29" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
@@ -912,7 +1076,7 @@
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
-          <t>Data Source</t>
+          <t>Source</t>
         </is>
       </c>
       <c r="D1" s="4" t="inlineStr">
@@ -942,7 +1106,7 @@
       </c>
       <c r="I1" s="4" t="inlineStr">
         <is>
-          <t>Revenue Tier</t>
+          <t>LE Qualified (&gt;$5B)</t>
         </is>
       </c>
       <c r="J1" s="4" t="inlineStr">
@@ -989,7 +1153,7 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -1017,7 +1181,7 @@
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>Mega (&gt;$50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J2" s="5" t="n"/>
@@ -1040,7 +1204,7 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D3" s="5" t="n"/>
@@ -1064,7 +1228,7 @@
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>Mega (&gt;$50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J3" s="5" t="n"/>
@@ -1087,7 +1251,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -1115,7 +1279,7 @@
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>Mega (&gt;$50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J4" s="5" t="n"/>
@@ -1138,7 +1302,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -1166,7 +1330,7 @@
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>Mega (&gt;$50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J5" s="5" t="n"/>
@@ -1189,7 +1353,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -1217,7 +1381,7 @@
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>Mega (&gt;$50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J6" s="5" t="n"/>
@@ -1240,7 +1404,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D7" s="5" t="n"/>
@@ -1264,7 +1428,7 @@
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>Mega (&gt;$50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J7" s="5" t="n"/>
@@ -1287,7 +1451,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -1315,7 +1479,7 @@
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>Mega (&gt;$50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J8" s="5" t="n"/>
@@ -1338,7 +1502,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -1366,7 +1530,7 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Mega (&gt;$50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J9" s="5" t="n"/>
@@ -1389,7 +1553,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -1417,7 +1581,7 @@
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>Mega (&gt;$50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J10" s="5" t="n"/>
@@ -1440,7 +1604,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -1468,7 +1632,7 @@
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>Mega (&gt;$50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J11" s="5" t="n"/>
@@ -1491,7 +1655,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -1519,7 +1683,7 @@
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>Mega (&gt;$50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J12" s="5" t="n"/>
@@ -1542,7 +1706,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -1570,7 +1734,7 @@
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J13" s="5" t="n"/>
@@ -1593,7 +1757,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -1621,7 +1785,7 @@
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J14" s="5" t="n"/>
@@ -1644,7 +1808,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D15" s="5" t="n"/>
@@ -1668,7 +1832,7 @@
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J15" s="5" t="n"/>
@@ -1691,7 +1855,7 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D16" s="5" t="n"/>
@@ -1715,7 +1879,7 @@
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J16" s="5" t="n"/>
@@ -1738,7 +1902,7 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -1766,7 +1930,7 @@
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J17" s="5" t="n"/>
@@ -1789,7 +1953,7 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -1817,7 +1981,7 @@
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J18" s="5" t="n"/>
@@ -1840,7 +2004,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -1868,7 +2032,7 @@
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J19" s="5" t="n"/>
@@ -1891,7 +2055,7 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -1919,7 +2083,7 @@
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J20" s="5" t="n"/>
@@ -1942,7 +2106,7 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D21" s="5" t="n"/>
@@ -1966,7 +2130,7 @@
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J21" s="5" t="n"/>
@@ -1989,7 +2153,7 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -2017,7 +2181,7 @@
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J22" s="5" t="n"/>
@@ -2040,7 +2204,7 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -2068,7 +2232,7 @@
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J23" s="5" t="n"/>
@@ -2091,7 +2255,7 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -2119,7 +2283,7 @@
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J24" s="5" t="n"/>
@@ -2142,7 +2306,7 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -2170,7 +2334,7 @@
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J25" s="5" t="n"/>
@@ -2193,7 +2357,7 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -2221,7 +2385,7 @@
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J26" s="5" t="n"/>
@@ -2244,7 +2408,7 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -2272,7 +2436,7 @@
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J27" s="5" t="n"/>
@@ -2295,7 +2459,7 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -2323,7 +2487,7 @@
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J28" s="5" t="n"/>
@@ -2346,7 +2510,7 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D29" s="5" t="n"/>
@@ -2370,7 +2534,7 @@
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J29" s="5" t="n"/>
@@ -2393,7 +2557,7 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D30" s="5" t="n"/>
@@ -2417,7 +2581,7 @@
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J30" s="5" t="n"/>
@@ -2440,7 +2604,7 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -2468,7 +2632,7 @@
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J31" s="5" t="n"/>
@@ -2491,7 +2655,7 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -2519,7 +2683,7 @@
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J32" s="5" t="n"/>
@@ -2542,7 +2706,7 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -2570,7 +2734,7 @@
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J33" s="5" t="n"/>
@@ -2593,7 +2757,7 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -2621,7 +2785,7 @@
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J34" s="5" t="n"/>
@@ -2644,7 +2808,7 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -2672,7 +2836,7 @@
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J35" s="5" t="n"/>
@@ -2695,7 +2859,7 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -2723,7 +2887,7 @@
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J36" s="5" t="n"/>
@@ -2746,7 +2910,7 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D37" s="5" t="n"/>
@@ -2770,7 +2934,7 @@
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J37" s="5" t="n"/>
@@ -2793,7 +2957,7 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -2821,7 +2985,7 @@
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J38" s="5" t="n"/>
@@ -2844,7 +3008,7 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D39" s="5" t="n"/>
@@ -2868,7 +3032,7 @@
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J39" s="5" t="n"/>
@@ -2891,7 +3055,7 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D40" s="5" t="n"/>
@@ -2915,7 +3079,7 @@
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J40" s="5" t="n"/>
@@ -2938,7 +3102,7 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -2966,7 +3130,7 @@
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J41" s="5" t="n"/>
@@ -2989,7 +3153,7 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -3017,7 +3181,7 @@
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J42" s="5" t="n"/>
@@ -3040,7 +3204,7 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -3068,7 +3232,7 @@
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J43" s="5" t="n"/>
@@ -3091,7 +3255,7 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -3119,7 +3283,7 @@
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J44" s="5" t="n"/>
@@ -3142,7 +3306,7 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -3170,7 +3334,7 @@
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J45" s="5" t="n"/>
@@ -3193,7 +3357,7 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D46" s="5" t="n"/>
@@ -3217,7 +3381,7 @@
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J46" s="5" t="n"/>
@@ -3240,7 +3404,7 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
@@ -3268,7 +3432,7 @@
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J47" s="5" t="n"/>
@@ -3291,7 +3455,7 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D48" s="5" t="n"/>
@@ -3315,7 +3479,7 @@
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J48" s="5" t="n"/>
@@ -3338,7 +3502,7 @@
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
@@ -3366,7 +3530,7 @@
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J49" s="5" t="n"/>
@@ -3389,7 +3553,7 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D50" s="5" t="n"/>
@@ -3413,7 +3577,7 @@
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J50" s="5" t="n"/>
@@ -3436,7 +3600,7 @@
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D51" s="5" t="n"/>
@@ -3460,7 +3624,7 @@
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J51" s="5" t="n"/>
@@ -3483,7 +3647,7 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
@@ -3511,7 +3675,7 @@
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J52" s="5" t="n"/>
@@ -3534,7 +3698,7 @@
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
@@ -3562,7 +3726,7 @@
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J53" s="5" t="n"/>
@@ -3585,7 +3749,7 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D54" s="5" t="n"/>
@@ -3609,7 +3773,7 @@
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J54" s="5" t="n"/>
@@ -3632,7 +3796,7 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -3660,7 +3824,7 @@
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J55" s="5" t="n"/>
@@ -3683,7 +3847,7 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D56" s="5" t="n"/>
@@ -3707,7 +3871,7 @@
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J56" s="5" t="n"/>
@@ -3730,7 +3894,7 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
@@ -3758,7 +3922,7 @@
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J57" s="5" t="n"/>
@@ -3781,7 +3945,7 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D58" s="5" t="n"/>
@@ -3805,7 +3969,7 @@
       </c>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J58" s="5" t="n"/>
@@ -3828,7 +3992,7 @@
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D59" s="5" t="n"/>
@@ -3852,7 +4016,7 @@
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J59" s="5" t="n"/>
@@ -3875,7 +4039,7 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
@@ -3903,7 +4067,7 @@
       </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J60" s="5" t="n"/>
@@ -3926,7 +4090,7 @@
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D61" s="5" t="n"/>
@@ -3950,7 +4114,7 @@
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J61" s="5" t="n"/>
@@ -3973,7 +4137,7 @@
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D62" s="5" t="n"/>
@@ -3997,7 +4161,7 @@
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J62" s="5" t="n"/>
@@ -4020,7 +4184,7 @@
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
@@ -4048,7 +4212,7 @@
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J63" s="5" t="n"/>
@@ -4071,7 +4235,7 @@
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
@@ -4099,7 +4263,7 @@
       </c>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J64" s="5" t="n"/>
@@ -4122,7 +4286,7 @@
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
@@ -4150,7 +4314,7 @@
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J65" s="5" t="n"/>
@@ -4173,7 +4337,7 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
@@ -4201,7 +4365,7 @@
       </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J66" s="5" t="n"/>
@@ -4224,7 +4388,7 @@
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
@@ -4252,7 +4416,7 @@
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J67" s="5" t="n"/>
@@ -4275,7 +4439,7 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
@@ -4303,7 +4467,7 @@
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J68" s="5" t="n"/>
@@ -4326,7 +4490,7 @@
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
@@ -4354,7 +4518,7 @@
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J69" s="5" t="n"/>
@@ -4377,7 +4541,7 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
@@ -4405,7 +4569,7 @@
       </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J70" s="5" t="n"/>
@@ -4428,7 +4592,7 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
@@ -4456,7 +4620,7 @@
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J71" s="5" t="n"/>
@@ -4479,7 +4643,7 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
@@ -4507,7 +4671,7 @@
       </c>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J72" s="5" t="n"/>
@@ -4530,7 +4694,7 @@
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
@@ -4558,7 +4722,7 @@
       </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J73" s="5" t="n"/>
@@ -4581,7 +4745,7 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D74" s="5" t="n"/>
@@ -4605,7 +4769,7 @@
       </c>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J74" s="5" t="n"/>
@@ -4628,7 +4792,7 @@
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D75" s="5" t="n"/>
@@ -4652,7 +4816,7 @@
       </c>
       <c r="I75" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J75" s="5" t="n"/>
@@ -4675,7 +4839,7 @@
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
@@ -4703,7 +4867,7 @@
       </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J76" s="5" t="n"/>
@@ -4726,7 +4890,7 @@
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
@@ -4754,7 +4918,7 @@
       </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J77" s="5" t="n"/>
@@ -4777,7 +4941,7 @@
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
@@ -4805,7 +4969,7 @@
       </c>
       <c r="I78" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J78" s="5" t="n"/>
@@ -4828,7 +4992,7 @@
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
@@ -4856,7 +5020,7 @@
       </c>
       <c r="I79" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J79" s="5" t="n"/>
@@ -4879,7 +5043,7 @@
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D80" s="5" t="n"/>
@@ -4903,7 +5067,7 @@
       </c>
       <c r="I80" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J80" s="5" t="n"/>
@@ -4926,7 +5090,7 @@
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
@@ -4954,7 +5118,7 @@
       </c>
       <c r="I81" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J81" s="5" t="n"/>
@@ -4977,7 +5141,7 @@
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
@@ -5005,7 +5169,7 @@
       </c>
       <c r="I82" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J82" s="5" t="n"/>
@@ -5028,7 +5192,7 @@
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D83" s="5" t="n"/>
@@ -5052,7 +5216,7 @@
       </c>
       <c r="I83" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J83" s="5" t="n"/>
@@ -5075,7 +5239,7 @@
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
@@ -5103,7 +5267,7 @@
       </c>
       <c r="I84" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J84" s="5" t="n"/>
@@ -5126,7 +5290,7 @@
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D85" s="5" t="n"/>
@@ -5150,7 +5314,7 @@
       </c>
       <c r="I85" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J85" s="5" t="n"/>
@@ -5173,7 +5337,7 @@
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
@@ -5201,7 +5365,7 @@
       </c>
       <c r="I86" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J86" s="5" t="n"/>
@@ -5224,7 +5388,7 @@
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D87" s="5" t="n"/>
@@ -5248,7 +5412,7 @@
       </c>
       <c r="I87" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J87" s="5" t="n"/>
@@ -5271,7 +5435,7 @@
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
@@ -5299,7 +5463,7 @@
       </c>
       <c r="I88" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J88" s="5" t="n"/>
@@ -5322,7 +5486,7 @@
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D89" s="5" t="n"/>
@@ -5346,7 +5510,7 @@
       </c>
       <c r="I89" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J89" s="5" t="n"/>
@@ -5369,7 +5533,7 @@
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D90" s="5" t="n"/>
@@ -5393,7 +5557,7 @@
       </c>
       <c r="I90" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J90" s="5" t="n"/>
@@ -5416,7 +5580,7 @@
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
@@ -5444,7 +5608,7 @@
       </c>
       <c r="I91" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J91" s="5" t="n"/>
@@ -5467,7 +5631,7 @@
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
@@ -5495,7 +5659,7 @@
       </c>
       <c r="I92" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J92" s="5" t="n"/>
@@ -5518,7 +5682,7 @@
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
@@ -5546,7 +5710,7 @@
       </c>
       <c r="I93" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J93" s="5" t="n"/>
@@ -5569,7 +5733,7 @@
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
@@ -5597,7 +5761,7 @@
       </c>
       <c r="I94" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J94" s="5" t="n"/>
@@ -5616,7 +5780,7 @@
       <c r="B95" s="5" t="n"/>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
@@ -5644,7 +5808,7 @@
       </c>
       <c r="I95" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J95" s="5" t="n"/>
@@ -5667,7 +5831,7 @@
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
@@ -5695,7 +5859,7 @@
       </c>
       <c r="I96" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J96" s="5" t="n"/>
@@ -5718,7 +5882,7 @@
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
@@ -5746,7 +5910,7 @@
       </c>
       <c r="I97" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J97" s="5" t="n"/>
@@ -5769,7 +5933,7 @@
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
@@ -5797,7 +5961,7 @@
       </c>
       <c r="I98" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J98" s="5" t="n"/>
@@ -5820,7 +5984,7 @@
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D99" s="5" t="n"/>
@@ -5844,7 +6008,7 @@
       </c>
       <c r="I99" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J99" s="5" t="n"/>
@@ -5867,7 +6031,7 @@
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D100" s="5" t="n"/>
@@ -5891,7 +6055,7 @@
       </c>
       <c r="I100" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J100" s="5" t="n"/>
@@ -5914,7 +6078,7 @@
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
@@ -5942,7 +6106,7 @@
       </c>
       <c r="I101" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J101" s="5" t="n"/>
@@ -5965,7 +6129,7 @@
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D102" s="5" t="n"/>
@@ -5989,7 +6153,7 @@
       </c>
       <c r="I102" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J102" s="5" t="n"/>
@@ -6012,7 +6176,7 @@
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
@@ -6040,7 +6204,7 @@
       </c>
       <c r="I103" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J103" s="5" t="n"/>
@@ -6063,7 +6227,7 @@
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
@@ -6091,7 +6255,7 @@
       </c>
       <c r="I104" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J104" s="5" t="n"/>
@@ -6114,7 +6278,7 @@
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
@@ -6142,7 +6306,7 @@
       </c>
       <c r="I105" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J105" s="5" t="n"/>
@@ -6165,7 +6329,7 @@
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
@@ -6193,7 +6357,7 @@
       </c>
       <c r="I106" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J106" s="5" t="n"/>
@@ -6216,7 +6380,7 @@
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
@@ -6244,7 +6408,7 @@
       </c>
       <c r="I107" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J107" s="5" t="n"/>
@@ -6267,7 +6431,7 @@
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
@@ -6295,7 +6459,7 @@
       </c>
       <c r="I108" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J108" s="5" t="n"/>
@@ -6318,7 +6482,7 @@
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D109" s="5" t="n"/>
@@ -6342,7 +6506,7 @@
       </c>
       <c r="I109" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J109" s="5" t="n"/>
@@ -6365,7 +6529,7 @@
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>NTT Only (Aashita/Ops)</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
@@ -6393,7 +6557,7 @@
       </c>
       <c r="I110" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J110" s="5" t="n"/>
@@ -6412,7 +6576,7 @@
       <c r="B111" s="5" t="n"/>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D111" s="5" t="n"/>
@@ -6463,7 +6627,7 @@
       <c r="B112" s="5" t="n"/>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D112" s="5" t="n"/>
@@ -6510,7 +6674,7 @@
       <c r="B113" s="5" t="n"/>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D113" s="5" t="n"/>
@@ -6561,7 +6725,7 @@
       <c r="B114" s="5" t="n"/>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D114" s="5" t="n"/>
@@ -6612,7 +6776,7 @@
       <c r="B115" s="5" t="n"/>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D115" s="5" t="n"/>
@@ -6663,7 +6827,7 @@
       <c r="B116" s="5" t="n"/>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D116" s="5" t="n"/>
@@ -6714,7 +6878,7 @@
       <c r="B117" s="5" t="n"/>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D117" s="5" t="n"/>
@@ -6765,7 +6929,7 @@
       <c r="B118" s="5" t="n"/>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D118" s="5" t="n"/>
@@ -6816,7 +6980,7 @@
       <c r="B119" s="5" t="n"/>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D119" s="5" t="n"/>
@@ -6867,7 +7031,7 @@
       <c r="B120" s="5" t="n"/>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D120" s="5" t="n"/>
@@ -6918,7 +7082,7 @@
       <c r="B121" s="5" t="n"/>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D121" s="5" t="n"/>
@@ -6969,7 +7133,7 @@
       <c r="B122" s="5" t="n"/>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D122" s="5" t="n"/>
@@ -7020,7 +7184,7 @@
       <c r="B123" s="5" t="n"/>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D123" s="5" t="n"/>
@@ -7071,7 +7235,7 @@
       <c r="B124" s="5" t="n"/>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D124" s="5" t="n"/>
@@ -7118,7 +7282,7 @@
       <c r="B125" s="5" t="n"/>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D125" s="5" t="n"/>
@@ -7165,7 +7329,7 @@
       <c r="B126" s="5" t="n"/>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D126" s="5" t="n"/>
@@ -7216,7 +7380,7 @@
       <c r="B127" s="5" t="n"/>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D127" s="5" t="n"/>
@@ -7267,7 +7431,7 @@
       <c r="B128" s="5" t="n"/>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D128" s="5" t="n"/>
@@ -7318,7 +7482,7 @@
       <c r="B129" s="5" t="n"/>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D129" s="5" t="n"/>
@@ -7369,7 +7533,7 @@
       <c r="B130" s="5" t="n"/>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D130" s="5" t="n"/>
@@ -7420,7 +7584,7 @@
       <c r="B131" s="5" t="n"/>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D131" s="5" t="n"/>
@@ -7471,7 +7635,7 @@
       <c r="B132" s="5" t="n"/>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D132" s="5" t="n"/>
@@ -7522,7 +7686,7 @@
       <c r="B133" s="5" t="n"/>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D133" s="5" t="n"/>
@@ -7573,7 +7737,7 @@
       <c r="B134" s="5" t="n"/>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D134" s="5" t="n"/>
@@ -7624,7 +7788,7 @@
       <c r="B135" s="5" t="n"/>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D135" s="5" t="n"/>
@@ -7675,7 +7839,7 @@
       <c r="B136" s="5" t="n"/>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D136" s="5" t="n"/>
@@ -7726,7 +7890,7 @@
       <c r="B137" s="5" t="n"/>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D137" s="5" t="n"/>
@@ -7777,7 +7941,7 @@
       <c r="B138" s="5" t="n"/>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D138" s="5" t="n"/>
@@ -7828,7 +7992,7 @@
       <c r="B139" s="5" t="n"/>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D139" s="5" t="n"/>
@@ -7879,7 +8043,7 @@
       <c r="B140" s="5" t="n"/>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D140" s="5" t="n"/>
@@ -7930,7 +8094,7 @@
       <c r="B141" s="5" t="n"/>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D141" s="5" t="n"/>
@@ -7977,7 +8141,7 @@
       <c r="B142" s="5" t="n"/>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D142" s="5" t="n"/>
@@ -8028,7 +8192,7 @@
       <c r="B143" s="5" t="n"/>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D143" s="5" t="n"/>
@@ -8079,7 +8243,7 @@
       <c r="B144" s="5" t="n"/>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D144" s="5" t="n"/>
@@ -8130,7 +8294,7 @@
       <c r="B145" s="5" t="n"/>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D145" s="5" t="n"/>
@@ -8181,7 +8345,7 @@
       <c r="B146" s="5" t="n"/>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D146" s="5" t="n"/>
@@ -8232,7 +8396,7 @@
       <c r="B147" s="5" t="n"/>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D147" s="5" t="n"/>
@@ -8283,7 +8447,7 @@
       <c r="B148" s="5" t="n"/>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D148" s="5" t="n"/>
@@ -8334,7 +8498,7 @@
       <c r="B149" s="5" t="n"/>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D149" s="5" t="n"/>
@@ -8385,7 +8549,7 @@
       <c r="B150" s="5" t="n"/>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D150" s="5" t="n"/>
@@ -8436,7 +8600,7 @@
       <c r="B151" s="5" t="n"/>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D151" s="5" t="n"/>
@@ -8487,7 +8651,7 @@
       <c r="B152" s="5" t="n"/>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D152" s="5" t="n"/>
@@ -8538,7 +8702,7 @@
       <c r="B153" s="5" t="n"/>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D153" s="5" t="n"/>
@@ -8589,7 +8753,7 @@
       <c r="B154" s="5" t="n"/>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D154" s="5" t="n"/>
@@ -8640,7 +8804,7 @@
       <c r="B155" s="5" t="n"/>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D155" s="5" t="n"/>
@@ -8691,7 +8855,7 @@
       <c r="B156" s="5" t="n"/>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D156" s="5" t="n"/>
@@ -8742,7 +8906,7 @@
       <c r="B157" s="5" t="n"/>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D157" s="5" t="n"/>
@@ -8793,7 +8957,7 @@
       <c r="B158" s="5" t="n"/>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D158" s="5" t="n"/>
@@ -8844,7 +9008,7 @@
       <c r="B159" s="5" t="n"/>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D159" s="5" t="n"/>
@@ -8895,7 +9059,7 @@
       <c r="B160" s="5" t="n"/>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D160" s="5" t="n"/>
@@ -8946,7 +9110,7 @@
       <c r="B161" s="5" t="n"/>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D161" s="5" t="n"/>
@@ -8997,7 +9161,7 @@
       <c r="B162" s="5" t="n"/>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D162" s="5" t="n"/>
@@ -9048,7 +9212,7 @@
       <c r="B163" s="5" t="n"/>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D163" s="5" t="n"/>
@@ -9099,7 +9263,7 @@
       <c r="B164" s="5" t="n"/>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D164" s="5" t="n"/>
@@ -9150,7 +9314,7 @@
       <c r="B165" s="5" t="n"/>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D165" s="5" t="n"/>
@@ -9201,7 +9365,7 @@
       <c r="B166" s="5" t="n"/>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D166" s="5" t="n"/>
@@ -9252,7 +9416,7 @@
       <c r="B167" s="5" t="n"/>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D167" s="5" t="n"/>
@@ -9303,7 +9467,7 @@
       <c r="B168" s="5" t="n"/>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D168" s="5" t="n"/>
@@ -9354,7 +9518,7 @@
       <c r="B169" s="5" t="n"/>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D169" s="5" t="n"/>
@@ -9401,7 +9565,7 @@
       <c r="B170" s="5" t="n"/>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D170" s="5" t="n"/>
@@ -9452,7 +9616,7 @@
       <c r="B171" s="5" t="n"/>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D171" s="5" t="n"/>
@@ -9503,7 +9667,7 @@
       <c r="B172" s="5" t="n"/>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D172" s="5" t="n"/>
@@ -9554,7 +9718,7 @@
       <c r="B173" s="5" t="n"/>
       <c r="C173" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D173" s="5" t="n"/>
@@ -9605,7 +9769,7 @@
       <c r="B174" s="5" t="n"/>
       <c r="C174" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D174" s="5" t="n"/>
@@ -9656,7 +9820,7 @@
       <c r="B175" s="5" t="n"/>
       <c r="C175" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D175" s="5" t="n"/>
@@ -9707,7 +9871,7 @@
       <c r="B176" s="5" t="n"/>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D176" s="5" t="n"/>
@@ -9758,7 +9922,7 @@
       <c r="B177" s="5" t="n"/>
       <c r="C177" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D177" s="5" t="n"/>
@@ -9809,7 +9973,7 @@
       <c r="B178" s="5" t="n"/>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D178" s="5" t="n"/>
@@ -9856,7 +10020,7 @@
       <c r="B179" s="5" t="n"/>
       <c r="C179" s="5" t="inlineStr">
         <is>
-          <t>SAP MOVE Only</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D179" s="5" t="n"/>
@@ -9911,7 +10075,7 @@
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>Both (NTT + SAP MOVE)</t>
+          <t>Both (Ops + SAP)</t>
         </is>
       </c>
       <c r="D180" s="5" t="inlineStr">
@@ -9939,7 +10103,7 @@
       </c>
       <c r="I180" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J180" s="5" t="inlineStr">
@@ -9984,7 +10148,7 @@
       </c>
       <c r="C181" s="5" t="inlineStr">
         <is>
-          <t>Both (NTT + SAP MOVE)</t>
+          <t>Both (Ops + SAP)</t>
         </is>
       </c>
       <c r="D181" s="5" t="inlineStr">
@@ -10012,7 +10176,7 @@
       </c>
       <c r="I181" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J181" s="5" t="inlineStr">
@@ -10057,7 +10221,7 @@
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>Both (NTT + SAP MOVE)</t>
+          <t>Both (Ops + SAP)</t>
         </is>
       </c>
       <c r="D182" s="5" t="inlineStr">
@@ -10085,7 +10249,7 @@
       </c>
       <c r="I182" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J182" s="5" t="inlineStr">
@@ -10130,7 +10294,7 @@
       </c>
       <c r="C183" s="5" t="inlineStr">
         <is>
-          <t>Both (NTT + SAP MOVE)</t>
+          <t>Both (Ops + SAP)</t>
         </is>
       </c>
       <c r="D183" s="5" t="inlineStr">
@@ -10158,7 +10322,7 @@
       </c>
       <c r="I183" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J183" s="5" t="inlineStr">
@@ -10203,7 +10367,7 @@
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>Both (NTT + SAP MOVE)</t>
+          <t>Both (Ops + SAP)</t>
         </is>
       </c>
       <c r="D184" s="5" t="inlineStr">
@@ -10231,7 +10395,7 @@
       </c>
       <c r="I184" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J184" s="5" t="inlineStr">
@@ -10272,7 +10436,7 @@
       </c>
       <c r="C185" s="5" t="inlineStr">
         <is>
-          <t>Both (NTT + SAP MOVE)</t>
+          <t>Both (Ops + SAP)</t>
         </is>
       </c>
       <c r="D185" s="5" t="inlineStr">
@@ -10300,7 +10464,7 @@
       </c>
       <c r="I185" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J185" s="5" t="inlineStr">
@@ -10343,7 +10507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -10351,9 +10515,10 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10384,15 +10549,20 @@
       </c>
       <c r="F1" s="6" t="inlineStr">
         <is>
+          <t>LE_Qualified</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
           <t>Avg_Revenue_USD</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>Total_Revenue_USD</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>Tier1_Count</t>
         </is>
@@ -10417,12 +10587,15 @@
         <v>0</v>
       </c>
       <c r="F2" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="G2" s="5" t="n">
         <v>62897580098.86562</v>
       </c>
-      <c r="G2" s="5" t="n">
+      <c r="H2" s="5" t="n">
         <v>817668541285.2531</v>
       </c>
-      <c r="H2" s="5" t="n">
+      <c r="I2" s="5" t="n">
         <v>5</v>
       </c>
     </row>
@@ -10445,12 +10618,15 @@
         <v>1</v>
       </c>
       <c r="F3" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="G3" s="5" t="n">
         <v>39782938102.5886</v>
       </c>
-      <c r="G3" s="5" t="n">
+      <c r="H3" s="5" t="n">
         <v>795658762051.772</v>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="I3" s="5" t="n">
         <v>6</v>
       </c>
     </row>
@@ -10473,12 +10649,15 @@
         <v>2</v>
       </c>
       <c r="F4" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="G4" s="5" t="n">
         <v>18882393346.35805</v>
       </c>
-      <c r="G4" s="5" t="n">
+      <c r="H4" s="5" t="n">
         <v>793060520547.038</v>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="I4" s="5" t="n">
         <v>9</v>
       </c>
     </row>
@@ -10501,12 +10680,15 @@
         <v>2</v>
       </c>
       <c r="F5" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" s="5" t="n">
         <v>55914768620.71033</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="H5" s="5" t="n">
         <v>167744305862.131</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="I5" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -10529,12 +10711,15 @@
         <v>0</v>
       </c>
       <c r="F6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" s="5" t="n">
         <v>25028591683.099</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="H6" s="5" t="n">
         <v>125142958415.495</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="I6" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -10557,12 +10742,15 @@
         <v>3</v>
       </c>
       <c r="F7" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" s="5" t="n">
         <v>26243250788.36425</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="H7" s="5" t="n">
         <v>104973003153.457</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="I7" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -10585,12 +10773,15 @@
         <v>0</v>
       </c>
       <c r="F8" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" s="5" t="n">
         <v>18573333333.33333</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="H8" s="5" t="n">
         <v>55720000000</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="I8" s="5" t="n">
         <v>3</v>
       </c>
     </row>
@@ -10613,12 +10804,15 @@
         <v>1</v>
       </c>
       <c r="F9" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" s="5" t="n">
         <v>11326007893.211</v>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="H9" s="5" t="n">
         <v>45304031572.844</v>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="I9" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10641,12 +10835,15 @@
         <v>0</v>
       </c>
       <c r="F10" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" s="5" t="n">
         <v>7714761213.7394</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="H10" s="5" t="n">
         <v>38573806068.697</v>
       </c>
-      <c r="H10" s="5" t="n">
+      <c r="I10" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -10669,12 +10866,15 @@
         <v>1</v>
       </c>
       <c r="F11" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" s="5" t="n">
         <v>11774591508.11833</v>
       </c>
-      <c r="G11" s="5" t="n">
+      <c r="H11" s="5" t="n">
         <v>35323774524.355</v>
       </c>
-      <c r="H11" s="5" t="n">
+      <c r="I11" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10697,12 +10897,15 @@
         <v>1</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>33000000000</v>
+        <v>1</v>
       </c>
       <c r="G12" s="5" t="n">
         <v>33000000000</v>
       </c>
       <c r="H12" s="5" t="n">
+        <v>33000000000</v>
+      </c>
+      <c r="I12" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10725,12 +10928,15 @@
         <v>1</v>
       </c>
       <c r="F13" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" s="5" t="n">
         <v>8021700171.568634</v>
       </c>
-      <c r="G13" s="5" t="n">
+      <c r="H13" s="5" t="n">
         <v>24065100514.7059</v>
       </c>
-      <c r="H13" s="5" t="n">
+      <c r="I13" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10753,12 +10959,15 @@
         <v>0</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>23194509773.059</v>
+        <v>1</v>
       </c>
       <c r="G14" s="5" t="n">
         <v>23194509773.059</v>
       </c>
       <c r="H14" s="5" t="n">
+        <v>23194509773.059</v>
+      </c>
+      <c r="I14" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10781,12 +10990,15 @@
         <v>0</v>
       </c>
       <c r="F15" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" s="5" t="n">
         <v>11117741065.5955</v>
       </c>
-      <c r="G15" s="5" t="n">
+      <c r="H15" s="5" t="n">
         <v>22235482131.191</v>
       </c>
-      <c r="H15" s="5" t="n">
+      <c r="I15" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10809,12 +11021,15 @@
         <v>1</v>
       </c>
       <c r="F16" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" s="5" t="n">
         <v>9130000000</v>
       </c>
-      <c r="G16" s="5" t="n">
+      <c r="H16" s="5" t="n">
         <v>18260000000</v>
       </c>
-      <c r="H16" s="5" t="n">
+      <c r="I16" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -10837,12 +11052,15 @@
         <v>0</v>
       </c>
       <c r="F17" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" s="5" t="n">
         <v>8700000000</v>
       </c>
-      <c r="G17" s="5" t="n">
+      <c r="H17" s="5" t="n">
         <v>17400000000</v>
       </c>
-      <c r="H17" s="5" t="n">
+      <c r="I17" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10865,12 +11083,15 @@
         <v>1</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>14765638211.654</v>
+        <v>1</v>
       </c>
       <c r="G18" s="5" t="n">
         <v>14765638211.654</v>
       </c>
       <c r="H18" s="5" t="n">
+        <v>14765638211.654</v>
+      </c>
+      <c r="I18" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10893,12 +11114,15 @@
         <v>0</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>8700000000</v>
+        <v>1</v>
       </c>
       <c r="G19" s="5" t="n">
         <v>8700000000</v>
       </c>
       <c r="H19" s="5" t="n">
+        <v>8700000000</v>
+      </c>
+      <c r="I19" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10921,7 +11145,7 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
     <col width="42" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -10953,7 +11177,7 @@
       </c>
       <c r="F1" s="7" t="inlineStr">
         <is>
-          <t>Revenue Tier</t>
+          <t>LE Qualified (&gt;$5B)</t>
         </is>
       </c>
       <c r="G1" s="7" t="inlineStr">
@@ -10988,7 +11212,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>Mega (&gt;$50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -11019,7 +11243,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>Mega (&gt;$50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -11054,7 +11278,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Mega (&gt;$50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -11089,7 +11313,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Mega (&gt;$50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -11124,7 +11348,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Mega (&gt;$50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -11155,7 +11379,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Mega (&gt;$50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -11190,7 +11414,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Mega (&gt;$50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -11225,7 +11449,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Mega (&gt;$50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -11260,7 +11484,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Mega (&gt;$50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -11295,7 +11519,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Mega (&gt;$50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -11330,7 +11554,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Mega (&gt;$50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -11365,7 +11589,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -11400,7 +11624,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -11431,7 +11655,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
@@ -11462,7 +11686,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -11497,7 +11721,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -11532,7 +11756,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -11567,7 +11791,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
@@ -11602,7 +11826,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
@@ -11633,7 +11857,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
@@ -11668,7 +11892,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -11703,7 +11927,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
@@ -11738,7 +11962,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -11773,7 +11997,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
@@ -11808,7 +12032,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
@@ -11843,7 +12067,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -11878,7 +12102,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
@@ -11909,7 +12133,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -11940,7 +12164,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
@@ -11975,7 +12199,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -12010,7 +12234,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
@@ -12045,7 +12269,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -12080,7 +12304,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
@@ -12115,7 +12339,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -12150,7 +12374,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
@@ -12181,7 +12405,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -12216,7 +12440,7 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
@@ -12247,7 +12471,7 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -12278,7 +12502,7 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -12313,7 +12537,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -12348,7 +12572,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
@@ -12383,7 +12607,7 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -12418,7 +12642,7 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>Tier 1 ($20-50B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
@@ -12453,7 +12677,7 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -12484,7 +12708,7 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
@@ -12519,7 +12743,7 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
@@ -12550,7 +12774,7 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
@@ -12585,7 +12809,7 @@
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
@@ -12616,7 +12840,7 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
@@ -12647,7 +12871,7 @@
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
@@ -12682,7 +12906,7 @@
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
@@ -12717,7 +12941,7 @@
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
@@ -12748,7 +12972,7 @@
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
@@ -12783,7 +13007,7 @@
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
@@ -12814,7 +13038,7 @@
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
@@ -12849,7 +13073,7 @@
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
@@ -12880,7 +13104,7 @@
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
@@ -12911,7 +13135,7 @@
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
@@ -12946,7 +13170,7 @@
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
@@ -12977,7 +13201,7 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
@@ -13008,7 +13232,7 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
@@ -13043,7 +13267,7 @@
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
@@ -13078,7 +13302,7 @@
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
@@ -13113,7 +13337,7 @@
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
@@ -13148,7 +13372,7 @@
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
@@ -13183,7 +13407,7 @@
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
@@ -13218,7 +13442,7 @@
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
@@ -13253,7 +13477,7 @@
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
@@ -13288,7 +13512,7 @@
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
@@ -13323,7 +13547,7 @@
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
@@ -13358,7 +13582,7 @@
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
@@ -13393,7 +13617,7 @@
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
@@ -13424,7 +13648,7 @@
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
@@ -13455,7 +13679,7 @@
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
@@ -13490,7 +13714,7 @@
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
@@ -13525,7 +13749,7 @@
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
@@ -13560,7 +13784,7 @@
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
@@ -13595,7 +13819,7 @@
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
@@ -13626,7 +13850,7 @@
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
@@ -13661,7 +13885,7 @@
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
@@ -13696,7 +13920,7 @@
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
@@ -13727,7 +13951,7 @@
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
@@ -13762,7 +13986,7 @@
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
@@ -13793,7 +14017,7 @@
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
@@ -13828,7 +14052,7 @@
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
@@ -13859,7 +14083,7 @@
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
@@ -13894,7 +14118,7 @@
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
@@ -13925,7 +14149,7 @@
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
@@ -13956,7 +14180,7 @@
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
@@ -13991,7 +14215,7 @@
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr">
@@ -14026,7 +14250,7 @@
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
@@ -14061,7 +14285,7 @@
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
@@ -14096,7 +14320,7 @@
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
@@ -14127,7 +14351,7 @@
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
@@ -14162,7 +14386,7 @@
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G96" s="5" t="inlineStr">
@@ -14197,7 +14421,7 @@
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
@@ -14232,7 +14456,7 @@
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
@@ -14263,7 +14487,7 @@
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
@@ -14294,7 +14518,7 @@
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
@@ -14329,7 +14553,7 @@
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
@@ -14360,7 +14584,7 @@
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
@@ -14395,7 +14619,7 @@
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
@@ -14430,7 +14654,7 @@
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G104" s="5" t="inlineStr">
@@ -14465,7 +14689,7 @@
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G105" s="5" t="inlineStr">
@@ -14500,7 +14724,7 @@
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr">
@@ -14535,7 +14759,7 @@
       </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
@@ -14570,7 +14794,7 @@
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G108" s="5" t="inlineStr">
@@ -14601,7 +14825,7 @@
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G109" s="5" t="inlineStr">
@@ -14636,7 +14860,7 @@
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G110" s="5" t="inlineStr">
@@ -16899,13 +17123,13 @@
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="42" customWidth="1" min="5" max="5"/>
     <col width="29" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
@@ -16927,7 +17151,7 @@
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
-          <t>Data Source</t>
+          <t>Source</t>
         </is>
       </c>
       <c r="D1" s="4" t="inlineStr">
@@ -16957,7 +17181,7 @@
       </c>
       <c r="I1" s="4" t="inlineStr">
         <is>
-          <t>Revenue Tier</t>
+          <t>LE Qualified (&gt;$5B)</t>
         </is>
       </c>
       <c r="J1" s="4" t="inlineStr">
@@ -17004,7 +17228,7 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>Both (NTT + SAP MOVE)</t>
+          <t>Both (Ops + SAP)</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -17032,7 +17256,7 @@
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J2" s="5" t="inlineStr">
@@ -17077,7 +17301,7 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Both (NTT + SAP MOVE)</t>
+          <t>Both (Ops + SAP)</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -17105,7 +17329,7 @@
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr">
@@ -17150,7 +17374,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Both (NTT + SAP MOVE)</t>
+          <t>Both (Ops + SAP)</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -17178,7 +17402,7 @@
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
@@ -17223,7 +17447,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Both (NTT + SAP MOVE)</t>
+          <t>Both (Ops + SAP)</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -17251,7 +17475,7 @@
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>Tier 3 ($5-10B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
@@ -17292,7 +17516,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Both (NTT + SAP MOVE)</t>
+          <t>Both (Ops + SAP)</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -17320,7 +17544,7 @@
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
@@ -17365,7 +17589,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Both (NTT + SAP MOVE)</t>
+          <t>Both (Ops + SAP)</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -17393,7 +17617,7 @@
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>Tier 2 ($10-20B)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
@@ -17436,7 +17660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -17446,7 +17670,8 @@
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
     <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17487,6 +17712,11 @@
       </c>
       <c r="H1" s="6" t="inlineStr">
         <is>
+          <t>LE Qualified (&gt;$5B)</t>
+        </is>
+      </c>
+      <c r="I1" s="6" t="inlineStr">
+        <is>
           <t>Priority Score</t>
         </is>
       </c>
@@ -17494,12 +17724,12 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Ministry of Manpower</t>
+          <t>ASE Singapore Pte Ltd</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>PRIME MINISTER'S OFFICE SINGAPORE</t>
+          <t>ASE Group</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -17519,25 +17749,30 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>Wholesale Distribution</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="G2" s="5" t="n">
-        <v>433541631368.306</v>
-      </c>
-      <c r="H2" s="5" t="n">
-        <v>8</v>
+        <v>18360000000</v>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>RGE Pte. Ltd.</t>
+          <t>DAIKIN ASIA SERVICING PTE LTD</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Royal Golden Eagle (RGE)</t>
+          <t>Daikin Industries Ltd</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -17557,25 +17792,30 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>Energy &amp; Utility</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="G3" s="5" t="n">
-        <v>40000000000</v>
-      </c>
-      <c r="H3" s="5" t="n">
+        <v>31300000000</v>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>DAIKIN ASIA SERVICING PTE LTD</t>
+          <t>RGE Pte. Ltd.</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Daikin Industries Ltd</t>
+          <t>Royal Golden Eagle (RGE)</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -17595,25 +17835,30 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Energy &amp; Utility</t>
         </is>
       </c>
       <c r="G4" s="5" t="n">
-        <v>31300000000</v>
-      </c>
-      <c r="H4" s="5" t="n">
+        <v>40000000000</v>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>TOYOTA MOTOR ASIA (SINGAPORE) PTE. LTD.</t>
+          <t>The Monetary Authority of Singapore</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>TOYOTA MOTOR CORPORATION</t>
+          <t>Government of Singapore</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -17633,25 +17878,30 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>BFSI</t>
         </is>
       </c>
       <c r="G5" s="5" t="n">
-        <v>23194509773.059</v>
-      </c>
-      <c r="H5" s="5" t="n">
+        <v>10700000000</v>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>MICRON SEMICONDUCTOR ASIA OPERATIONS PTE. LTD.</t>
+          <t>Ministry of Manpower</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>PRIME MINISTER'S OFFICE SINGAPORE</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -17671,25 +17921,30 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>High Tech</t>
+          <t>Wholesale Distribution</t>
         </is>
       </c>
       <c r="G6" s="5" t="n">
-        <v>25418286301.418</v>
-      </c>
-      <c r="H6" s="5" t="n">
+        <v>433541631368.306</v>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>KENNAMETAL DISTRIBUTION SERVICES ASIA PTE. LTD.</t>
+          <t>SINGAPORE POOLS (PRIVATE) LIMITED</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Kennametal Inc.</t>
+          <t>Tote Board (Parent), Singapore Pools Ltd</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -17709,25 +17964,30 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Wholesale Distribution</t>
+          <t>Hospitality</t>
         </is>
       </c>
       <c r="G7" s="5" t="n">
-        <v>42956502489.942</v>
-      </c>
-      <c r="H7" s="5" t="n">
+        <v>12200000000</v>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>APPLIED MATERIALS SOUTH EAST ASIA PTE. LTD.</t>
+          <t>United Overseas Bank Limited</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Applied Materials, Inc.</t>
+          <t>UNITED OVERSEAS BANK LIMITED</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -17747,25 +18007,30 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Wholesale Distribution</t>
+          <t>BFSI</t>
         </is>
       </c>
       <c r="G8" s="5" t="n">
-        <v>21661554736.114</v>
-      </c>
-      <c r="H8" s="5" t="n">
+        <v>17550471390.088</v>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>GLENCORE SINGAPORE PTE. LTD.</t>
+          <t>TOYOTA MOTOR ASIA (SINGAPORE) PTE. LTD.</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>GLENCORE PLC</t>
+          <t>TOYOTA MOTOR CORPORATION</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -17785,25 +18050,30 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Energy &amp; Utility</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="G9" s="5" t="n">
-        <v>39116007105.512</v>
-      </c>
-      <c r="H9" s="5" t="n">
+        <v>23194509773.059</v>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Lazada South East Asia Pte Ltd</t>
+          <t>MICRON SEMICONDUCTOR ASIA OPERATIONS PTE. LTD.</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Lazada Group (Alibaba Group Holding)</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -17813,7 +18083,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Managed Services Potential</t>
+          <t>Migration Target</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -17823,30 +18093,35 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>High Tech</t>
         </is>
       </c>
       <c r="G10" s="5" t="n">
-        <v>130350000000</v>
-      </c>
-      <c r="H10" s="5" t="n">
+        <v>25418286301.418</v>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>ADITYA BIRLA GLOBAL TRADING (SINGAPORE)</t>
+          <t>KENNAMETAL DISTRIBUTION SERVICES ASIA PTE. LTD.</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Aditya Birla group</t>
+          <t>Kennametal Inc.</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -17861,25 +18136,30 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>BFSI</t>
+          <t>Wholesale Distribution</t>
         </is>
       </c>
       <c r="G11" s="5" t="n">
-        <v>67846864420.541</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>6</v>
+        <v>42956502489.942</v>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>SINGAPORE POOLS (PRIVATE) LIMITED</t>
+          <t>GLENCORE SINGAPORE PTE. LTD.</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Tote Board (Parent), Singapore Pools Ltd</t>
+          <t>GLENCORE PLC</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -17899,30 +18179,35 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Hospitality</t>
+          <t>Energy &amp; Utility</t>
         </is>
       </c>
       <c r="G12" s="5" t="n">
-        <v>12200000000</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>6</v>
+        <v>39116007105.512</v>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>APPLE SOUTH ASIA PTE. LTD.</t>
+          <t>APPLIED MATERIALS SOUTH EAST ASIA PTE. LTD.</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
+          <t>Applied Materials, Inc.</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -17941,26 +18226,31 @@
         </is>
       </c>
       <c r="G13" s="5" t="n">
-        <v>111486267590.537</v>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>6</v>
+        <v>21661554736.114</v>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Temasek</t>
+          <t>MITSUBISHI CORPORATION RTM INTERNATIONAL PTE. LTD.</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>PRIME MINISTER'S OFFICE SINGAPORE</t>
+          <t>MITSUBISHI CORPORATION</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -17975,30 +18265,35 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>BFSI</t>
+          <t>Wholesale Distribution</t>
         </is>
       </c>
       <c r="G14" s="5" t="n">
-        <v>125888300000</v>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>6</v>
+        <v>6019569055.884</v>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>TOTALENERGIES TRADING ASIA PTE. LTD.</t>
+          <t>PHILLIPS 66 INTERNATIONAL TRADING PTE. LTD.</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>TOTALENERGIES SE</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -18017,21 +18312,26 @@
         </is>
       </c>
       <c r="G15" s="5" t="n">
-        <v>50288164952.649</v>
-      </c>
-      <c r="H15" s="5" t="n">
-        <v>6</v>
+        <v>11762654370.869</v>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Mitsubishi Heavy Industries Engine</t>
+          <t>CARGILL INTERNATIONAL TRADING PTE LTD</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Mitsubishi Heavy Industries Ltd</t>
+          <t>Cargill, Incorporated</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -18041,7 +18341,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Managed Services Potential</t>
+          <t>Migration Target</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -18051,25 +18351,30 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>BFSI</t>
         </is>
       </c>
       <c r="G16" s="5" t="n">
-        <v>33000000000</v>
-      </c>
-      <c r="H16" s="5" t="n">
-        <v>6</v>
+        <v>11568075190.347</v>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>ASE Singapore Pte Ltd</t>
+          <t>Infineon Technologies Asia Pacific Pte L td</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>ASE Group</t>
+          <t>Infineon Technologies AG</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -18089,25 +18394,30 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>High Tech</t>
         </is>
       </c>
       <c r="G17" s="5" t="n">
-        <v>18360000000</v>
-      </c>
-      <c r="H17" s="5" t="n">
-        <v>6</v>
+        <v>11250827006.495</v>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Bridgestone Asia Pacific Pte. Ltd. [BRIDGESTONE SINGAPORE PTE LTD]</t>
+          <t>INPEX ENERGY TRADING SINGAPORE PTE. LTD.</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>BRIDGESTONE CORPORATION</t>
+          <t>INPEX CORPORATION</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -18117,7 +18427,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Managed Services Potential</t>
+          <t>Migration Target</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -18127,25 +18437,30 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Professional Services</t>
+          <t>Energy &amp; Utility</t>
         </is>
       </c>
       <c r="G18" s="5" t="n">
-        <v>28949785383.422</v>
-      </c>
-      <c r="H18" s="5" t="n">
-        <v>6</v>
+        <v>11382065057.42</v>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>United Overseas Bank Limited</t>
+          <t>WANHUA CHEMICAL (SINGAPORE) PTE. LTD.</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>UNITED OVERSEAS BANK LIMITED</t>
+          <t>Wanhua Chemical Group Co., Ltd.</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -18165,25 +18480,30 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>BFSI</t>
+          <t>Wholesale Distribution</t>
         </is>
       </c>
       <c r="G19" s="5" t="n">
-        <v>17550471390.088</v>
-      </c>
-      <c r="H19" s="5" t="n">
-        <v>6</v>
+        <v>11469953643.609</v>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>The Monetary Authority of Singapore</t>
+          <t>MITSUI &amp; CO. ENERGY TRADING SINGAPORE PTE. LTD.</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Government of Singapore</t>
+          <t>MITSUI &amp; CO., LTD.</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -18203,30 +18523,35 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>BFSI</t>
+          <t>Energy &amp; Utility</t>
         </is>
       </c>
       <c r="G20" s="5" t="n">
-        <v>10700000000</v>
-      </c>
-      <c r="H20" s="5" t="n">
-        <v>6</v>
+        <v>13466329742.237</v>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>SK ENERGY INTERNATIONAL PTE. LTD.</t>
+          <t>ENEOS OIL &amp; ENERGY ASIA PTE. LTD.</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>SK Inc.</t>
+          <t>ENEOS HOLDINGS, INC.</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -18241,30 +18566,35 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Energy &amp; Utility</t>
+          <t>Energy &amp; Utilities</t>
         </is>
       </c>
       <c r="G21" s="5" t="n">
-        <v>28469727197.15</v>
-      </c>
-      <c r="H21" s="5" t="n">
-        <v>6</v>
+        <v>5996806068.697</v>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>PETROCHINA INTERNATIONAL (SINGAPORE) PTE. LTD.</t>
+          <t>BAOHUA STEEL HOLDINGS PTE. LIMITED</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>China National Petroleum Corporation</t>
+          <t>BAOHUA STEEL HOLDINGS PTE. LIMITED</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -18279,30 +18609,35 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Energy &amp; Utility</t>
+          <t>BFSI</t>
         </is>
       </c>
       <c r="G22" s="5" t="n">
-        <v>35604720494.508</v>
-      </c>
-      <c r="H22" s="5" t="n">
-        <v>6</v>
+        <v>8466584669.615</v>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>SINOCHEM INTERNATIONAL OIL (SINGAPORE) PTE LTD</t>
+          <t>LOUIS DREYFUS COMPANY ASIA  PTE. LTD.</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Sinochem Holdings Corporation Ltd.</t>
+          <t>Akira Holding Foundation</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -18317,30 +18652,35 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Energy &amp; Utility</t>
+          <t>BFSI</t>
         </is>
       </c>
       <c r="G23" s="5" t="n">
-        <v>28533760646.53</v>
-      </c>
-      <c r="H23" s="5" t="n">
-        <v>6</v>
+        <v>7082145276.971</v>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>FLEX LTD.</t>
+          <t>AMKOR TECHNOLOGY SINGAPORE HOLDING PTE. LTD.</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>FLEX LTD.</t>
+          <t>Amkor Technology, Inc.</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -18355,30 +18695,35 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Wholesale Distribution</t>
+          <t>BFSI</t>
         </is>
       </c>
       <c r="G24" s="5" t="n">
-        <v>26705062908.256</v>
-      </c>
-      <c r="H24" s="5" t="n">
-        <v>6</v>
+        <v>6335330182.739</v>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>ARAMCO TRADING SINGAPORE PTE. LTD.</t>
+          <t>COFCO INTERNATIONAL SINGAPORE PTE. LTD.</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>GOVERNMENT OF SAUDI ARABIA</t>
+          <t>COFCO Corporation</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -18393,30 +18738,35 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Professional Services</t>
+          <t>BFSI</t>
         </is>
       </c>
       <c r="G25" s="5" t="n">
-        <v>56268035631.894</v>
-      </c>
-      <c r="H25" s="5" t="n">
-        <v>6</v>
+        <v>5760293695.592</v>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>FOXCONN SINGAPORE PTE LTD</t>
+          <t>Senoko Energy Pte Ltd</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>HON HAI PRECISION INDUSTRY CO., LTD.</t>
+          <t>MARUBENI CORPORATION</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -18431,25 +18781,30 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>Wholesale Distribution</t>
+          <t>Energy &amp; Utilities</t>
         </is>
       </c>
       <c r="G26" s="5" t="n">
-        <v>51788445962.471</v>
-      </c>
-      <c r="H26" s="5" t="n">
-        <v>6</v>
+        <v>10000000000</v>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>NTUC Enterprise Co-operative Limited [NTUC INCOME INSURANCE CO-OPERATIVE LTD]</t>
+          <t>YTL PowerSeraya Pte. Limited</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>NTUC ENTERPRISE CO-OPERATIVE LTD</t>
+          <t>YTL Cayman Limited</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -18469,14 +18824,19 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>BFSI</t>
         </is>
       </c>
       <c r="G27" s="5" t="n">
-        <v>6140000000</v>
-      </c>
-      <c r="H27" s="5" t="n">
-        <v>6</v>
+        <v>6670000000</v>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="28">
@@ -18513,19 +18873,24 @@
       <c r="G28" s="5" t="n">
         <v>5410000000</v>
       </c>
-      <c r="H28" s="5" t="n">
-        <v>6</v>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Infineon Technologies Asia Pacific Pte L td</t>
+          <t>Nippon Paint Holdings SG Pte. Ltd.</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Infineon Technologies AG</t>
+          <t>Nippon Paint Holdings</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -18545,27 +18910,28 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>High Tech</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="G29" s="5" t="n">
-        <v>11250827006.495</v>
-      </c>
-      <c r="H29" s="5" t="n">
-        <v>6</v>
+        <v>8700000000</v>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>MITSUBISHI CORPORATION RTM INTERNATIONAL PTE. LTD.</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>MITSUBISHI CORPORATION</t>
-        </is>
-      </c>
+          <t>Olympus</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n"/>
       <c r="C30" s="5" t="inlineStr">
         <is>
           <t>Tier 1</t>
@@ -18583,14 +18949,19 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Wholesale Distribution</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="G30" s="5" t="n">
-        <v>6019569055.884</v>
-      </c>
-      <c r="H30" s="5" t="n">
-        <v>6</v>
+        <v>6060000000</v>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="31">
@@ -18627,8 +18998,13 @@
       <c r="G31" s="5" t="n">
         <v>12420000000</v>
       </c>
-      <c r="H31" s="5" t="n">
-        <v>6</v>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
